--- a/marketer_forms/001_sweepstake_entry_form--marketer_forms.xlsx
+++ b/marketer_forms/001_sweepstake_entry_form--marketer_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -713,7 +713,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Select one</t>
+          <t>Select One With No Options</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -736,7 +736,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Select multiple</t>
+          <t>Select Multiple With No Options</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -754,12 +754,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>select_one_with_no_options</t>
+          <t>select_one_with_no_options_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Select one</t>
+          <t>Select One With No Options 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -777,12 +777,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>select_multiple_with_no_options</t>
+          <t>select_multiple_with_no_options_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Select multiple</t>
+          <t>Select Multiple With No Options 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -938,12 +938,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>email_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -984,12 +984,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>note_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Note 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Text2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1035,7 +1035,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Select one</t>
+          <t>Select One2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Select multiple</t>
+          <t>Select Multiple2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Select one</t>
+          <t>Select One3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1102,12 +1102,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="41" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="43" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1220,29 +1220,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>select_one_with_no_options_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1254,29 +1254,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one_with_no_options_choices</t>
+          <t>select_multiple_with_no_options_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1288,97 +1288,97 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple_with_no_options_choices</t>
+          <t>select_one_with_no_options_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one_with_no_options_choices</t>
+          <t>select_one_with_no_options_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one_with_no_options_choices</t>
+          <t>select_multiple_with_no_options_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple_with_no_options_choices</t>
+          <t>select_multiple_with_no_options_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_multiple_with_no_options_choices</t>
+          <t>select_one2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1407,12 +1407,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1441,29 +1441,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_one3_choices</t>
+          <t>select_multiple2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1475,10 +1475,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>select_one3_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
         <is>
           <t>No</t>
         </is>
